--- a/astro-site/public/dl/haccp-templates/17-cooling-thawing-log.xlsx
+++ b/astro-site/public/dl/haccp-templates/17-cooling-thawing-log.xlsx
@@ -24,11 +24,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="h:mm AM/PM"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="m/d/yyyy h:mm AM/PM"/>
+    <numFmt numFmtId="168" formatCode="m/d/yy h:mm AM/PM"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -175,13 +176,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -612,7 +615,7 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Covers the two moments when food passes slowly through the danger zone (between 135 °F and 41 °F), which is where bacteria multiply. The hazard analysis (template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs)) points to these two sheets.</t>
+          <t>Covers the two moments when food passes slowly through the danger zone (between 135 °F and 41 °F), which is where bacteria multiply. The hazard analysis in template 12 (HACCP Plan) points to these two sheets.</t>
         </is>
       </c>
     </row>
@@ -626,7 +629,7 @@
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>▸ Rule, in two stages (Food Code §3-501.14): from 135 °F to 70 °F or below within 2 hours, then to 41 °F or below within 6 hours in total. It is the critical limit in template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs). UK: below 46 °F (8 °C) within 90 minutes (FSA, Safer Food Better Business).</t>
+          <t>▸ Rule, in two stages (Food Code §3-501.14): from 135 °F to 70 °F or below within 2 hours, then to 41 °F or below within 6 hours in total. It is the critical limit in template 12 (HACCP Plan). UK: below 46 °F (8 °C) within 90 minutes (FSA, Safer Food Better Business).</t>
         </is>
       </c>
     </row>
@@ -647,7 +650,7 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>▸ If it says ALERT: divide the product into shallow pans or discard it, and open the incident in template 11 (Corrective Action Log).</t>
+          <t>▸ If it says ALERT: discard the product and open the incident in template 11 (Corrective Action Log). If you catch it before the 2-hour mark still above 70 °F, reheat it to 165 °F and restart cooling with a faster method (shallow pans, ice bath, blast chiller).</t>
         </is>
       </c>
     </row>
@@ -661,7 +664,7 @@
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>▸ Rule: in the refrigerator at 41 °F or below (Food Code §3-501.13), covered and on a tray, and the product in use within the hours set in cell B3 (24 by default) from the START of thawing. It is the same critical limit that appears in template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs) for this CCP.</t>
+          <t>▸ Rule: in the refrigerator at 41 °F or below (Food Code §3-501.13), covered and on a tray, and the product in use within the hours set in cell B3 (24 by default) from the START of thawing. It is the same critical limit that appears in template 12 (HACCP Plan) for this CCP.</t>
         </is>
       </c>
     </row>
@@ -760,7 +763,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Month: _______________    135 °F to 70 °F or below within 2 hours, then to 41 °F or below within 6 hours in total (critical limit of this establishment's HACCP plan; see template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs)).</t>
+          <t>Month: _______________    135 °F to 70 °F or below within 2 hours, then to 41 °F or below within 6 hours in total. Critical limit of this establishment's HACCP plan: see template 12 (HACCP Plan).</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1657,7 @@
     <row r="46" ht="24.5" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>Enter the time and temperature at the start and measure again at TWO hours and at SIX hours. If at 2 h the product has not dropped to 70 °F or below, or at 6 h to 41 °F or below, the "Status" column says ALERT: divide the product into smaller, shallower containers or discard it, and open the incident in template 11 (Corrective Action Log).</t>
+          <t>Enter the time and temperature at the start and measure again at TWO hours and at SIX hours. If at 2 h the product has not dropped to 70 °F or below, or at 6 h to 41 °F or below, the "Status" column says ALERT: discard the product and open the incident in template 11 (Corrective Action Log). If you catch it before the 2-hour mark still above 70 °F, reheat it to 165 °F and restart cooling with a faster method (shallow pans, ice bath, blast chiller).</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1783,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Max. thawing time (hours):</t>
@@ -2618,7 +2621,7 @@
     <row r="46" ht="24.5" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>The sheet gives OK when the cooler is at 41 °F or below AND the product goes into use within the hours set in cell B3 (24 by default) from the START of thawing. It is the same criterion declared by the hazard analysis (template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs)), and it limits the total time the product spends in the danger zone. Large items need longer: allow about 24 h per 4-5 lb (USDA FSIS) and raise B3. A thawed product is NOT refrozen (house rule of this kit).</t>
+          <t>The sheet gives OK when the cooler is at 41 °F or below AND the product goes into use within the hours set in cell B3 (24 by default) from the START of thawing. It is the same criterion declared by the hazard analysis in template 12 (HACCP Plan). Large items need longer: allow about 24 h per 4-5 lb (USDA FSIS) and raise B3. A thawed product is NOT refrozen (house rule of this kit).</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2635,7 @@
     <row r="48" ht="12.2" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>Thawing at room temperature is a Priority foundation violation (§3-501.13): it appears as such in the health inspection checklist (template 15 (Health Inspection Self-Checklist)) and as a CCP in the hazard analysis (template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs)).</t>
+          <t>Thawing at room temperature is a Priority foundation violation (§3-501.13): it appears as such in the health inspection checklist, template 15 (Health Inspection Self-Checklist), and as a CCP in the hazard analysis, template 12 (HACCP Plan).</t>
         </is>
       </c>
     </row>
